--- a/processing_scripts/Inventory_Processing/2022 Metadata Creation/Source_Water_Metadata_Jun2022_Event.xlsx
+++ b/processing_scripts/Inventory_Processing/2022 Metadata Creation/Source_Water_Metadata_Jun2022_Event.xlsx
@@ -13,10 +13,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={65deb527-f365-4bb3-89b0-40f0d7ffd40f}</author>
+    <author>tc={10af678a-45fc-4e64-8066-e9a1ebb9e830}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{65deb527-f365-4bb3-89b0-40f0d7ffd40f}" ref="D14">
+    <comment authorId="0" xr:uid="{10af678a-45fc-4e64-8066-e9a1ebb9e830}" ref="D14">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -205,35 +205,35 @@
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="167" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="167" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="166" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -260,9 +260,9 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="opal.otenburg@gmail.com" id="{8b086c0f-aa38-4d93-af6b-fc644314277a}" userId="opal.otenburg@gmail.com" providerId="google-sheets"/>
-  <x18tc:person displayName="opal.otenburg@pnnl.gov" id="{ca70ef68-a66b-447c-a79a-33eefce2e60f}" userId="opal.otenburg@pnnl.gov" providerId="google-sheets"/>
-  <x18tc:person displayName="Allison Myers-Pigg" id="{884b0f02-3bf0-41be-b150-5560e8dd3975}" providerId="google-sheets"/>
+  <x18tc:person displayName="Allison Myers-Pigg" id="{5a4b9cdb-aa6f-441b-a039-85eff3d4a3db}" providerId="google-sheets"/>
+  <x18tc:person displayName="opal.otenburg@gmail.com" id="{c2f02ded-3e26-4ccc-84d7-88f1ba0288dc}" userId="opal.otenburg@gmail.com" providerId="google-sheets"/>
+  <x18tc:person displayName="opal.otenburg@pnnl.gov" id="{eda09608-be51-4445-bdb0-4fb72cdf083b}" userId="opal.otenburg@pnnl.gov" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -462,14 +462,14 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="D14" dT="2022-06-25T11:02:04.00" personId="{884b0f02-3bf0-41be-b150-5560e8dd3975}" id="{65deb527-f365-4bb3-89b0-40f0d7ffd40f}" done="0">
+  <x18tc:threadedComment ref="D14" dT="2022-06-25T11:02:04.00" personId="{5a4b9cdb-aa6f-441b-a039-85eff3d4a3db}" id="{10af678a-45fc-4e64-8066-e9a1ebb9e830}" done="0">
     <x18tc:text xml:space="preserve">@opal.otenburg@gmail.com @opal.otenburg@pnnl.gov  Were these vials corrected? If so, please also correct this column. thanks!</x18tc:text>
     <x18tc:mentions>
-      <x18tc:mention mentionpersonId="{8b086c0f-aa38-4d93-af6b-fc644314277a}" mentionId="{9e858b59-ac10-4fc1-afde-9d407784c5ec}" startIndex="0" length="24"/>
-      <x18tc:mention mentionpersonId="{ca70ef68-a66b-447c-a79a-33eefce2e60f}" mentionId="{35fac549-bd99-4abc-b944-f4f336f07468}" startIndex="25" length="23"/>
+      <x18tc:mention mentionpersonId="{c2f02ded-3e26-4ccc-84d7-88f1ba0288dc}" mentionId="{ce1ec601-79a2-4069-9951-cea5a6f3491e}" startIndex="0" length="24"/>
+      <x18tc:mention mentionpersonId="{eda09608-be51-4445-bdb0-4fb72cdf083b}" mentionId="{02fa1453-63cc-4834-a86e-799db94bf178}" startIndex="25" length="23"/>
     </x18tc:mentions>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="D14" dT="2022-07-08T16:08:56.00" personId="{884b0f02-3bf0-41be-b150-5560e8dd3975}" id="{ececfb02-95a0-48a7-8360-951fcbf8d013}" parentId="{65deb527-f365-4bb3-89b0-40f0d7ffd40f}">
+  <x18tc:threadedComment ref="D14" dT="2022-07-08T16:08:56.00" personId="{5a4b9cdb-aa6f-441b-a039-85eff3d4a3db}" id="{0c6a1f9f-f33c-4292-af7c-fb46413a6ed3}" parentId="{10af678a-45fc-4e64-8066-e9a1ebb9e830}">
     <x18tc:text xml:space="preserve">Change from Hr 6 to Hr 7</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
